--- a/06_Dev testing align/DEVINT_PHASE_0_3_AUDIT_TRACKER.xlsx
+++ b/06_Dev testing align/DEVINT_PHASE_0_3_AUDIT_TRACKER.xlsx
@@ -577,7 +577,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GapLogTable" displayName="GapLogTable" ref="A4:Q66" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GapLogTable" displayName="GapLogTable" ref="A4:Q87" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="Gap ID"/>
     <x:tableColumn id="2" name="Audit ID"/>
@@ -911,7 +911,7 @@
       </x:c>
       <x:c r="E6" s="73" t="n">
         <x:f>COUNTIF('Screen Inventory'!$K$5:$K$100,"Confirmed")</x:f>
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="66"/>
       <x:c r="G6" s="66"/>
@@ -930,7 +930,7 @@
       </x:c>
       <x:c r="E7" s="73" t="n">
         <x:f>COUNTIF('Screen Inventory'!$K$5:$K$100,"Waiting BA")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="66"/>
       <x:c r="G7" s="66"/>
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="E9" s="73" t="n">
         <x:f>COUNTIF('Screen Inventory'!$K$5:$K$100,"Not Started")</x:f>
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="66"/>
       <x:c r="G9" s="66"/>
@@ -979,7 +979,7 @@
         <x:v>Last updated</x:v>
       </x:c>
       <x:c r="B10" s="75" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="C10" s="66"/>
       <x:c r="D10" s="71" t="str">
@@ -987,7 +987,7 @@
       </x:c>
       <x:c r="E10" s="73" t="n">
         <x:f>COUNTIF('Screen Inventory'!$K$5:$K$100,"Blocked")</x:f>
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="66"/>
       <x:c r="G10" s="66"/>
@@ -1002,7 +1002,7 @@
       </x:c>
       <x:c r="E11" s="73" t="n">
         <x:f>COUNTA('Gap Log'!$B$5:$B$200)</x:f>
-        <x:v>62</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F11" s="66"/>
       <x:c r="G11" s="66"/>
@@ -1017,7 +1017,7 @@
       </x:c>
       <x:c r="E12" s="76" t="n">
         <x:f>COUNTIF('Gap Log'!$O$5:$O$200,"Pass")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="66"/>
       <x:c r="G12" s="66"/>
@@ -1516,10 +1516,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K8" s="91" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Retest Passed</x:v>
       </x:c>
       <x:c r="L8" s="91" t="str">
-        <x:v>Gap Confirmed</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M8" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A8)</x:f>
@@ -1529,10 +1529,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O8" s="92" t="str">
-        <x:v>BA classification: Team filter when selecting a Team = NOT TESTED. Project switching, All Teams project scoping, Team selection control and refresh persistence passed, but Team Alpha and Team Beta each returned 0 Work Items. Retest with a team-linked DEVINT-AUDIT item during Phase 1 create testing.</x:v>
+        <x:v>Retest 2026-07-24: Team Alpha now linked to NXP; selecting Team Alpha returns 8 items vs All Teams 11. Team filter works.</x:v>
       </x:c>
       <x:c r="P8" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1669,10 +1669,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K11" s="91" t="str">
-        <x:v>Waiting BA</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L11" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Accepted As-Is</x:v>
       </x:c>
       <x:c r="M11" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A11)</x:f>
@@ -1682,10 +1682,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O11" s="92" t="str">
-        <x:v>Project list data, aggregates, key/name search, status filters, empty state and row actions pass. BA approved adding Start Date like mockup/SRS. Linked Team display is NOT TESTED until dev finishes Team code. Permission exclusion, populated Archived filter and pagination also remain NOT TESTED. Projects/Lead wording remains pending BA.</x:v>
+        <x:v>Project list data, aggregates, key/name search, status filters, empty state and row actions pass. BA approved adding Start Date like mockup/SRS. BA 2026-07-24: accepted 'Projects' heading/breadcrumb wording as-is and Owner rename is done, so GAP-P0-PRJ-001 is closed (DevInt Accepted) - no BA item remains. Still NOT TESTED (blocked on dev / manual): Linked Team display (dev Team code), permission exclusion, populated Archived filter, pagination.</x:v>
       </x:c>
       <x:c r="P11" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1720,10 +1720,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K12" s="91" t="str">
-        <x:v>Waiting BA</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L12" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M12" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A12)</x:f>
@@ -1733,10 +1733,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O12" s="92" t="str">
-        <x:v>Created controlled Project AUD719 successfully with Hieu Vu Minh Bui as Owner, Team Alpha and description; counts, duplicate-key rejection and immutable key passed. BA approved Project Name 2-255 validation and Project Key 2-10 uppercase alphanumeric. Project Start Date persistence remains NOT TESTED. BA reported a confirmed UI defect: the last-row Edit action is clipped by the lower table/viewport boundary.</x:v>
+        <x:v>Created controlled Project AUD719 successfully with Hieu Vu Minh Bui as Owner, Team Alpha and description; counts, duplicate-key rejection and immutable key passed. BA approved Project Name 2-255 validation and Project Key 2-10 uppercase alphanumeric. BA 2026-07-24: Manage Projects wording accepted as-is (no BA item remains). Still open: confirmed UI defect - last-row Edit action clipped by the lower table/viewport boundary (Dev to fix); Project Start Date persistence remains NOT TESTED (needs manual date-picker retest).</x:v>
       </x:c>
       <x:c r="P12" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1822,10 +1822,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K14" s="91" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L14" s="91" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M14" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A14)</x:f>
@@ -1835,10 +1835,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O14" s="92" t="str">
-        <x:v>BA deferred Team list/search/filter verification until Team development and representative Team data are complete. This is a dependency block, not a confirmed defect.</x:v>
+        <x:v>Audit 2026-07-24: Teams list renders Key/Team/Project/Status/Lead/Updated + Search + Project/Status filters (1 team).</x:v>
       </x:c>
       <x:c r="P14" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1873,23 +1873,23 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K15" s="91" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L15" s="91" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M15" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A15)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N15" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O15" s="92" t="str">
-        <x:v>BA deferred Team create/edit/deactivate/restore verification until Team development and representative Team data are complete. This is a dependency block, not a confirmed defect.</x:v>
+        <x:v>Audit 2026-07-24: Create Team form has Name/Key(max10)/Projects(required)/Lead/Members/Status. Create fails 422 when Lead empty (GAP-P1-TEAM-001). Full lifecycle not exercised.</x:v>
       </x:c>
       <x:c r="P15" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2128,10 +2128,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K20" s="91" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Retest Passed</x:v>
       </x:c>
       <x:c r="L20" s="91" t="str">
-        <x:v>Fix Direction Approved</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M20" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A20)</x:f>
@@ -2141,10 +2141,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O20" s="92" t="str">
-        <x:v>P1-CREATE-02 executed against mockup and DevInt. Mockup passed: Create with details created exactly one Story US-4822, opened the same ID in Detail, persisted NXP/Core Platform/Marcus Webb/Estimate 0, defaulted Schedule State and Flow State to Idea, and showed one matching Backlog row. DevInt remained blocked by the confirmed Project/Team create defect, did not navigate, and created no matching record.</x:v>
+        <x:v>Retest 2026-07-24: Create with details creates one item (US-10), navigates to Detail, no duplicate. Default state Defined (GAP-P1-CREATE-009).</x:v>
       </x:c>
       <x:c r="P20" s="93" t="n">
-        <x:v>46222</x:v>
+        <x:v>46227</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2281,10 +2281,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="K23" s="91" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Retest Passed</x:v>
       </x:c>
       <x:c r="L23" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M23" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A23)</x:f>
@@ -2294,10 +2294,10 @@
         <x:v>Codex + BA</x:v>
       </x:c>
       <x:c r="O23" s="92" t="str">
-        <x:v>P1-TASK-01 fix directions are confirmed. P1-TASK-02 cannot be executed on DevInt because Task State is static on Dashboard and existing TA routes do not open Task Detail. Resume after either mutation surface is implemented.</x:v>
+        <x:v>Retest 2026-07-23 on new build: completing all child Tasks auto-moves parent to Completed (Schedule+Flow); reopening a Task auto-moves parent back to In-Progress (Schedule+Flow); To Do no longer zeroed on complete. Roll-up now passes.</x:v>
       </x:c>
       <x:c r="P23" s="93" t="n">
-        <x:v>46223</x:v>
+        <x:v>46226</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="104" customHeight="1">
@@ -2383,10 +2383,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K25" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L25" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M25" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A25)</x:f>
@@ -2395,7 +2395,9 @@
       <x:c r="N25" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O25" s="92"/>
+      <x:c r="O25" s="92" t="str">
+        <x:v>Audit 2026-07-24: WI has Description/Attachments/Notes/Release Notes; Task has Description/Notes/Attachments (no Release Notes). Match. Viewer read-only/XSS/upload not tested.</x:v>
+      </x:c>
       <x:c r="P25" s="93"/>
     </x:row>
     <x:row r="26">
@@ -2430,10 +2432,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K26" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L26" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M26" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A26)</x:f>
@@ -2442,7 +2444,9 @@
       <x:c r="N26" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O26" s="92"/>
+      <x:c r="O26" s="92" t="str">
+        <x:v>Audit 2026-07-24: Revision History works (newest-first, Time/Actor/Action/Details, logs create+state). Gaps: dup/mislabeled state log (GAP-P1-HIST-001); Task activity not logged (GAP-P1-HIST-002).</x:v>
+      </x:c>
       <x:c r="P26" s="93"/>
     </x:row>
     <x:row r="27">
@@ -2477,10 +2481,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="K27" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Gap</x:v>
       </x:c>
       <x:c r="L27" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M27" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A27)</x:f>
@@ -2489,7 +2493,9 @@
       <x:c r="N27" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O27" s="92"/>
+      <x:c r="O27" s="92" t="str">
+        <x:v>Audit 2026-07-24: selection bar works (2 Items Selected / Deselect All) but offers only Delete and Copy. Bulk assign Release (FR-015) and Iteration (FR-015A) are missing; Delete/Copy are not in the P2.1 contract. Manage Filters stays Accepted As-Is / Future Backlog (GAP-P1-BL-006).</x:v>
+      </x:c>
       <x:c r="P27" s="93"/>
     </x:row>
     <x:row r="28">
@@ -2524,10 +2530,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K28" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L28" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M28" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A28)</x:f>
@@ -2536,7 +2542,9 @@
       <x:c r="N28" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O28" s="92"/>
+      <x:c r="O28" s="92" t="str">
+        <x:v>Audit 2026-07-24: create modal matches (Type/Project/Team/Name/Start/End/State, default Planning, Create + Create with details); type selector, search and filters present. List is missing Project and Task Estimate columns (FR-005).</x:v>
+      </x:c>
       <x:c r="P28" s="93"/>
     </x:row>
     <x:row r="29">
@@ -2571,10 +2579,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="K29" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L29" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M29" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A29)</x:f>
@@ -2583,7 +2591,9 @@
       <x:c r="N29" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O29" s="92"/>
+      <x:c r="O29" s="92" t="str">
+        <x:v>Audit 2026-07-24: full-page detail with Theme + Notes editors, right panel Project/Team/Start/End/State/Planned Velocity, scope items panel and Commit/Accept controls. Minor: extra Revision History tab vs FR-017; unsaved-changes banner appears on load.</x:v>
+      </x:c>
       <x:c r="P29" s="93"/>
     </x:row>
     <x:row r="30">
@@ -2618,10 +2628,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="K30" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L30" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M30" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A30)</x:f>
@@ -2630,7 +2640,9 @@
       <x:c r="N30" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O30" s="92"/>
+      <x:c r="O30" s="92" t="str">
+        <x:v>Audit 2026-07-24: selector (name+dates), options from Timeboxes filtered by context, prev/next, dropdown, refresh on change and Story/Defect-only rows all pass. Missing Type column (FR-018); has forbidden per-row Defects column (FR-019); exposes a Board view toggle.</x:v>
+      </x:c>
       <x:c r="P30" s="93"/>
     </x:row>
     <x:row r="31">
@@ -2665,10 +2677,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K31" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L31" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M31" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A31)</x:f>
@@ -2677,7 +2689,9 @@
       <x:c r="N31" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O31" s="92"/>
+      <x:c r="O31" s="92" t="str">
+        <x:v>Audit 2026-07-24 with purpose-built data (IT-3/US-11/TA-7/TA-8): 2 Active Tasks correct; Totals 5 Points / 6 Hours / 5 Hours correct; Iteration End day count, Accepted points/percent and Defects count all correct. Minor: Planned Velocity shows "5 of 0 Points" when velocity is unset.</x:v>
+      </x:c>
       <x:c r="P31" s="93"/>
     </x:row>
     <x:row r="32" ht="112" customHeight="1">
@@ -2763,10 +2777,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="K33" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L33" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M33" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A33)</x:f>
@@ -2775,7 +2789,9 @@
       <x:c r="N33" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O33" s="92"/>
+      <x:c r="O33" s="92" t="str">
+        <x:v>Audit 2026-07-24: completing all child Tasks auto-Completed US-11 (Schedule + Flow mirrored); setting US-11 to Accepted auto-changed IT-3 from Planning to Accepted. Manual state control remains available. DEV-021 from the E2E pack does not reproduce.</x:v>
+      </x:c>
       <x:c r="P33" s="93"/>
     </x:row>
     <x:row r="34">
@@ -2810,10 +2826,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L34" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M34" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A34)</x:f>
@@ -2822,8 +2838,12 @@
       <x:c r="N34" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O34" s="92"/>
-      <x:c r="P34" s="93"/>
+      <x:c r="O34" s="92" t="str">
+        <x:v>7 findings logged for Team Status: 4 Gap (extra Search/Filters/Show Fields/pagination not in approved mockup; wrong breadcrumb ACME Corp &amp;gt; Team Status instead of [Project] &amp;gt; Track &amp;gt; Team status) + 3 Partial (State control is an icon toggle not a dropdown with 2/3 labels invisible; Estimate/ToDo/Actuals show dash instead of 0 default; Task Dashboard state labels Define/In Progress/Complete not exact catalog wording). Parent auto-complete (all Tasks Completed -&amp;gt; parent Completed) and reopen-to-In-Progress roll-up confirmed working live on US-8/TA-6. Reopen from Accepted (US-11/TA-8) does not revert parent - logged Pending BA. See GAP-P3-TS-001..007.</x:v>
+      </x:c>
+      <x:c r="P34" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="91" t="str">
@@ -2857,10 +2877,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="K35" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial Match</x:v>
       </x:c>
       <x:c r="L35" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M35" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A35)</x:f>
@@ -2869,8 +2889,12 @@
       <x:c r="N35" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O35" s="92"/>
-      <x:c r="P35" s="93"/>
+      <x:c r="O35" s="92" t="str">
+        <x:v>Create Release modal (Type locked to Release, State Planning/Active/Accepted only) and Release detail layout (Theme/Notes/Release Notes rich text, right panel with Start/Release Date, Project, State, Planned Velocity, Plan Estimate, Task Roll-up, Accepted, Version) all confirmed working live on new Release RE-2. A Burndown chart widget is present on Release detail, which violates the explicit no-Release-Progress-in-3.2 rule (FR-037). See GAP-P3-REL-001.</x:v>
+      </x:c>
+      <x:c r="P35" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="91" t="str">
@@ -2904,10 +2928,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K36" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Gap</x:v>
       </x:c>
       <x:c r="L36" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M36" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A36)</x:f>
@@ -2916,8 +2940,12 @@
       <x:c r="N36" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O36" s="92"/>
-      <x:c r="P36" s="93"/>
+      <x:c r="O36" s="92" t="str">
+        <x:v>Assigned US-11 to RE-2 from the Backlog Release picker; Backlog Release column and the Release list Task Est. roll-up both updated correctly (6h), but Release Detail RE-2 &amp;gt; Artifacts tab stayed empty (&amp;quot;No artifacts linked to this release&amp;quot;) even after a hard page reload. This blocks reassignment-refresh testing (FR-031/036/038) entirely. See GAP-P3-REL-002. US-11 restored to unassigned/Accepted after the test.</x:v>
+      </x:c>
+      <x:c r="P36" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="91" t="str">
@@ -2951,10 +2979,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="K37" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L37" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M37" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A37)</x:f>
@@ -2963,8 +2991,12 @@
       <x:c r="N37" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O37" s="92"/>
-      <x:c r="P37" s="93"/>
+      <x:c r="O37" s="92" t="str">
+        <x:v>Milestone create modal (6 status values Planned/At Risk/Met/Missed/Cancelled/Completed) and Details tab (Description/Notes left, Projects/Teams/Releases count-summary + Owner + Target dates + Status right panel) confirmed working live on new Milestone MS-2. Projects summary opens a searchable multi-select modal and the selection persists after Save. The Releases-link control was not independently re-clicked this session (same UI pattern as Projects, assumed equivalent) - flag for a quick confirm on retest.</x:v>
+      </x:c>
+      <x:c r="P37" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="91" t="str">
@@ -2998,10 +3030,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K38" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L38" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M38" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A38)</x:f>
@@ -3010,8 +3042,12 @@
       <x:c r="N38" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O38" s="92"/>
-      <x:c r="P38" s="93"/>
+      <x:c r="O38" s="92" t="str">
+        <x:v>Audit 2026-07-24 (P3-MS-02 retest): PASS / Match. Tested on MS-2 by linking Release RE-1 (Start 2026-07-01 / Release 2026-07-31). Target Start Date correctly derived to the earliest linked Release start (2026-07-01) and Target End Date to the latest Release date (2026-07-31); both became read-only with a &amp;quot;Derived from linked Releases&amp;quot; label (FR-013). Removing the Release link made both dates manually editable again and kept the last value without inferring a new one. Minor note: derivation only recalculates on Save - the unsaved edit preview still shows the old manual value momentarily. MS-2 test data reverted (Release unlinked).</x:v>
+      </x:c>
+      <x:c r="P38" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="91" t="str">
@@ -3045,10 +3081,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="K39" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Gap</x:v>
       </x:c>
       <x:c r="L39" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M39" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A39)</x:f>
@@ -3057,8 +3093,12 @@
       <x:c r="N39" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O39" s="92"/>
-      <x:c r="P39" s="93"/>
+      <x:c r="O39" s="92" t="str">
+        <x:v>No Add Artifact control anywhere on the Milestone Artifacts tab (only a search box and empty state). Work Item Detail Milestones field is static text (&amp;quot;No milestones&amp;quot;) with zero interactive control - confirmed via accessibility tree, no button/multi-select exists at all. Milestone-to-Work-Item assignment appears unimplemented from both directions. See GAP-P3-MS-001 and GAP-P3-MS-002.</x:v>
+      </x:c>
+      <x:c r="P39" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="91" t="str">
@@ -3092,10 +3132,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="K40" s="91" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Gap</x:v>
       </x:c>
       <x:c r="L40" s="91" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Gap Confirmed</x:v>
       </x:c>
       <x:c r="M40" s="91" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A40)</x:f>
@@ -3104,8 +3144,12 @@
       <x:c r="N40" s="91" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O40" s="92"/>
-      <x:c r="P40" s="93"/>
+      <x:c r="O40" s="92" t="str">
+        <x:v>Dashboard columns (Rank/ID/Name/User Story/Severity/Priority/State/Flow State/Fixed In Build/Iteration/Submitted By/Owner), Defect State transition-restricted options (matches the SRS state machine table exactly, better than the literal AC), Flow State independence (all 6 values), and Severity/Priority option sets all confirmed correct on DE-1/DE-2/DE-3. Creating a Defect from Quality &amp;gt; Defect silently fails: filled Name+Severity+Priority, submitted, modal closed with no error but no new row appeared and the Open Defects KPI stayed at 3. Reproduced twice. See GAP-P3-QA-001.</x:v>
+      </x:c>
+      <x:c r="P40" s="93" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
@@ -3139,10 +3183,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Match Confirmed</x:v>
       </x:c>
       <x:c r="M41" t="n">
         <x:f>COUNTIF('Gap Log'!$B$5:$B$200,A41)</x:f>
@@ -3151,8 +3195,12 @@
       <x:c r="N41" t="str">
         <x:v>Codex + BA</x:v>
       </x:c>
-      <x:c r="O41"/>
-      <x:c r="P41"/>
+      <x:c r="O41" t="str">
+        <x:v>Audit 2026-07-24 (P3-QA-02 retest): PASS / Match. Tested on DE-2. Changing Flow State from the Quality &amp;gt; Defect dashboard (Defined -&amp;gt; In-Progress) mirrored the Detail Schedule State to In-Progress; changing Schedule State on the Detail (In-Progress -&amp;gt; Completed) mirrored Flow State to Completed - two-way mirror confirmed. Defect State stayed Submitted throughout (independent, FR-016). Quality dashboard and Detail stayed consistent across both changes. Positive delta vs the 2026-07-20 E2E-11 finding DEV-020 (07_Test Business tracker) which reported no mirror and missing Idea/Release options: Flow State now offers all 6 values and mirrors both ways. Minor note: mirror recalculates on Save, not live in the unsaved preview. DE-2 reverted to Schedule/Flow = Defined, State = Submitted.</x:v>
+      </x:c>
+      <x:c r="P41" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3411,10 +3459,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N6" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O6" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23</x:v>
       </x:c>
       <x:c r="P6" s="95" t="str">
         <x:v>notes/P0-SHELL-01.md</x:v>
@@ -3464,10 +3512,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N7" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O7" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23</x:v>
       </x:c>
       <x:c r="P7" s="95" t="str">
         <x:v>notes/P0-SHELL-01.md</x:v>
@@ -3517,10 +3565,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N8" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O8" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23</x:v>
       </x:c>
       <x:c r="P8" s="95" t="str">
         <x:v>notes/P0-SHELL-01.md</x:v>
@@ -3570,10 +3618,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N9" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O9" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23</x:v>
       </x:c>
       <x:c r="P9" s="95" t="str">
         <x:v>notes/P0-SHELL-01.md</x:v>
@@ -3623,10 +3671,10 @@
         <x:v>Data / Config</x:v>
       </x:c>
       <x:c r="N10" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O10" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-24 - Team Alpha linked to NXP; Team filter returns 8 items vs 11 All Teams</x:v>
       </x:c>
       <x:c r="P10" s="95" t="str">
         <x:v>notes/P0-SHELL-02.md</x:v>
@@ -3729,10 +3777,10 @@
         <x:v>Business Rule / FE / Docs</x:v>
       </x:c>
       <x:c r="N12" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O12" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23</x:v>
       </x:c>
       <x:c r="P12" s="95" t="str">
         <x:v>notes/P0-WS-01.md</x:v>
@@ -3829,16 +3877,16 @@
         <x:v>Rename the DevInt heading/breadcrumb entry to Manage Projects where it represents the administration screen, and rename Lead to Owner. Keep the underlying route and stable identity unchanged.</x:v>
       </x:c>
       <x:c r="L14" s="95" t="str">
-        <x:v>Pending BA</x:v>
+        <x:v>DevInt Accepted</x:v>
       </x:c>
       <x:c r="M14" s="95" t="str">
         <x:v>FE / Docs</x:v>
       </x:c>
       <x:c r="N14" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Not Required</x:v>
       </x:c>
       <x:c r="O14" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - Owner fixed, heading still Projects. BA 2026-07-24: accepted the 'Projects' heading/breadcrumb as-is (screenshot reviewed); Owner rename already done, so this wording gap is closed - no Dev change required.</x:v>
       </x:c>
       <x:c r="P14" s="95" t="str">
         <x:v>notes/P0-PRJ-01.md</x:v>
@@ -3888,10 +3936,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N15" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O15" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23</x:v>
       </x:c>
       <x:c r="P15" s="95" t="str">
         <x:v>notes/P0-PRJ-01.md</x:v>
@@ -3994,10 +4042,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N17" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O17" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Create enabled with 1-char name</x:v>
       </x:c>
       <x:c r="P17" s="95" t="str">
         <x:v>notes/P0-PRJ-02.md</x:v>
@@ -4047,10 +4095,10 @@
         <x:v>Business Rule / FE / Docs</x:v>
       </x:c>
       <x:c r="N18" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O18" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - helper still 2-6 letters</x:v>
       </x:c>
       <x:c r="P18" s="95" t="str">
         <x:v>notes/P0-PRJ-02.md</x:v>
@@ -4153,10 +4201,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N20" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Blocked (retest)</x:v>
       </x:c>
       <x:c r="O20" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Not Retestable 2026-07-23 - only 2 project rows</x:v>
       </x:c>
       <x:c r="P20" s="95" t="str">
         <x:v>evidence/P0-PRJ-02/GAP-P0-PRJ-007-bottom-row-edit-clipped.png</x:v>
@@ -4365,10 +4413,10 @@
         <x:v>FE / Mockup / Docs</x:v>
       </x:c>
       <x:c r="N24" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O24" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - Email added; Teams+Last Login still missing</x:v>
       </x:c>
       <x:c r="P24" s="95" t="str">
         <x:v>notes/P1-USER-01.md</x:v>
@@ -4418,10 +4466,10 @@
         <x:v>FE / Mockup</x:v>
       </x:c>
       <x:c r="N25" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O25" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23</x:v>
       </x:c>
       <x:c r="P25" s="95" t="str">
         <x:v>notes/P1-USER-01.md</x:v>
@@ -4471,10 +4519,10 @@
         <x:v>FE / Mockup / Docs</x:v>
       </x:c>
       <x:c r="N26" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O26" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23</x:v>
       </x:c>
       <x:c r="P26" s="95" t="str">
         <x:v>notes/P1-USER-01.md</x:v>
@@ -4571,22 +4619,22 @@
         <x:v>Dev team should inspect the User Management API response and workspace-membership mapping, remove duplicate response rows or clean duplicate test membership data, and add a uniqueness regression test. No schema change is requested by BA.</x:v>
       </x:c>
       <x:c r="L28" s="95" t="str">
-        <x:v>Investigation Required</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="M28" s="95" t="str">
         <x:v>Dev / Data</x:v>
       </x:c>
       <x:c r="N28" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O28" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - duplicate admin resolved</x:v>
       </x:c>
       <x:c r="P28" s="95" t="str">
         <x:v>notes/P1-USER-01.md</x:v>
       </x:c>
       <x:c r="Q28" s="95" t="str">
-        <x:v>BA requested this be retained and reported to dev for investigation. Observed twice in the same 12-member DevInt list on 2026-07-19.</x:v>
+        <x:v>BA requested this be retained and reported to dev for investigation. Observed twice in the same 12-member DevInt list on 2026-07-19. BA 2026-07-24: closed as Fixed - retest 2026-07-23 showed the duplicate Admin User row resolved. Dev to keep the uniqueness regression test.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4736,10 +4784,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N31" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O31" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - no Priority filter</x:v>
       </x:c>
       <x:c r="P31" s="95" t="str">
         <x:v>notes/P1-BL-01.md</x:v>
@@ -4789,10 +4837,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N32" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Blocked (retest)</x:v>
       </x:c>
       <x:c r="O32" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Not Retestable 2026-07-23 - only 8 items</x:v>
       </x:c>
       <x:c r="P32" s="95" t="str">
         <x:v>notes/P1-BL-01.md</x:v>
@@ -4895,10 +4943,10 @@
         <x:v>FE / Mockup / Docs</x:v>
       </x:c>
       <x:c r="N34" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O34" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - two fields + In-Progress ok; control-type swapped</x:v>
       </x:c>
       <x:c r="P34" s="95" t="str">
         <x:v>notes/P1-BL-01.md</x:v>
@@ -5107,10 +5155,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N38" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O38" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - inline Title shows saved value immediately</x:v>
       </x:c>
       <x:c r="P38" s="95" t="str">
         <x:v>notes/P1-BL-02.md</x:v>
@@ -5266,10 +5314,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N41" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O41" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Project field in quick-create</x:v>
       </x:c>
       <x:c r="P41" s="95" t="str">
         <x:v>notes/P1-CREATE-01.md</x:v>
@@ -5319,10 +5367,10 @@
         <x:v>FE / API / Data</x:v>
       </x:c>
       <x:c r="N42" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O42" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - No team still offered</x:v>
       </x:c>
       <x:c r="P42" s="95" t="str">
         <x:v>evidence/P1-CREATE-01/P1-CREATE-01-devint-create-error.png</x:v>
@@ -5372,10 +5420,10 @@
         <x:v>FE / API / Docs</x:v>
       </x:c>
       <x:c r="N43" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O43" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - create succeeds with linked Team; No team still offered</x:v>
       </x:c>
       <x:c r="P43" s="95" t="str">
         <x:v>evidence/P1-CREATE-01/P1-CREATE-01-devint-create-error.png</x:v>
@@ -5478,10 +5526,10 @@
         <x:v>FE / API / BA / Docs</x:v>
       </x:c>
       <x:c r="N45" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O45" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Owner still defaults No Entry</x:v>
       </x:c>
       <x:c r="P45" s="95" t="str">
         <x:v>notes/P1-CREATE-01.md</x:v>
@@ -5531,10 +5579,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N46" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O46" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - Create with details button present; full flow not retested</x:v>
       </x:c>
       <x:c r="P46" s="95" t="str">
         <x:v>notes/P1-CREATE-02.md</x:v>
@@ -5584,10 +5632,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N47" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O47" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - fields persist; default state Defined not Idea (GAP-P1-CREATE-009)</x:v>
       </x:c>
       <x:c r="P47" s="95" t="str">
         <x:v>notes/P1-CREATE-02.md</x:v>
@@ -5637,10 +5685,10 @@
         <x:v>FE / BA</x:v>
       </x:c>
       <x:c r="N48" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O48" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Defects tab + Linked Items + Comments still present</x:v>
       </x:c>
       <x:c r="P48" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5690,10 +5738,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N49" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O49" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Project field added to Detail</x:v>
       </x:c>
       <x:c r="P49" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5743,10 +5791,10 @@
         <x:v>FE / BA / Docs</x:v>
       </x:c>
       <x:c r="N50" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O50" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Release single dropdown</x:v>
       </x:c>
       <x:c r="P50" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5796,10 +5844,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N51" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O51" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Milestones field added</x:v>
       </x:c>
       <x:c r="P51" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5849,10 +5897,10 @@
         <x:v>FE / BA / Docs</x:v>
       </x:c>
       <x:c r="N52" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O52" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - catalog 6 + In-Progress ok; control-type swapped</x:v>
       </x:c>
       <x:c r="P52" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5902,10 +5950,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N53" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O53" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Schedule/Flow mirror not working</x:v>
       </x:c>
       <x:c r="P53" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -5955,10 +6003,10 @@
         <x:v>FE / BA / Docs</x:v>
       </x:c>
       <x:c r="N54" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O54" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Owner default No Entry</x:v>
       </x:c>
       <x:c r="P54" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -6008,10 +6056,10 @@
         <x:v>FE / API</x:v>
       </x:c>
       <x:c r="N55" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O55" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - No team still offered</x:v>
       </x:c>
       <x:c r="P55" s="95" t="str">
         <x:v>notes/P1-WID-01.md</x:v>
@@ -6114,10 +6162,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N57" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O57" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - inline-save revert class fixed via BL-009; Iteration inline control not isolated this run</x:v>
       </x:c>
       <x:c r="P57" s="95" t="str">
         <x:v>notes/P2-IS-03.md</x:v>
@@ -6167,10 +6215,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N58" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O58" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - direct /iteration-status load shows data, no false empty state (warm session)</x:v>
       </x:c>
       <x:c r="P58" s="95" t="str">
         <x:v>notes/P2-IS-03.md</x:v>
@@ -6220,10 +6268,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N59" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O59" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - badge count matches child Tasks</x:v>
       </x:c>
       <x:c r="P59" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6273,10 +6321,10 @@
         <x:v>FE / API contract</x:v>
       </x:c>
       <x:c r="N60" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O60" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Task create works, inherits context</x:v>
       </x:c>
       <x:c r="P60" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6326,10 +6374,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N61" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O61" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - inline State + Owner controls present</x:v>
       </x:c>
       <x:c r="P61" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6379,10 +6427,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N62" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O62" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Task ID routes to Task Detail</x:v>
       </x:c>
       <x:c r="P62" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6432,10 +6480,10 @@
         <x:v>FE</x:v>
       </x:c>
       <x:c r="N63" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O63" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Task Create with details still absent</x:v>
       </x:c>
       <x:c r="P63" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6485,10 +6533,10 @@
         <x:v>FE / Business Rule</x:v>
       </x:c>
       <x:c r="N64" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partial (retest)</x:v>
       </x:c>
       <x:c r="O64" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Partial 2026-07-23 - states present; labels Define/Complete not exact catalog</x:v>
       </x:c>
       <x:c r="P64" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6538,10 +6586,10 @@
         <x:v>Business Rule / FE / Mockup</x:v>
       </x:c>
       <x:c r="N65" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Still Open</x:v>
       </x:c>
       <x:c r="O65" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Still Open 2026-07-23 - Task Owner default No Entry</x:v>
       </x:c>
       <x:c r="P65" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6591,10 +6639,10 @@
         <x:v>FE / Business Rule / Mockup</x:v>
       </x:c>
       <x:c r="N66" s="95" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Fixed (retest)</x:v>
       </x:c>
       <x:c r="O66" s="95" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Passed 2026-07-23 - Estimate = To Do + Actuals, read-only derived (5h)</x:v>
       </x:c>
       <x:c r="P66" s="95" t="str">
         <x:v>notes/P1-TASK-01.md</x:v>
@@ -6603,404 +6651,1118 @@
         <x:v>BA confirmed the formula on 2026-07-20. Dynamic retest is blocked by missing Task inline edit and Task Detail.</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="90"/>
-      <x:c r="B67" s="90"/>
-      <x:c r="C67" s="90"/>
-      <x:c r="D67" s="90"/>
-      <x:c r="E67" s="90"/>
-      <x:c r="F67" s="95"/>
-      <x:c r="G67" s="95"/>
-      <x:c r="H67" s="95"/>
-      <x:c r="I67" s="90"/>
-      <x:c r="J67" s="90"/>
-      <x:c r="K67" s="95"/>
-      <x:c r="L67" s="95"/>
-      <x:c r="M67" s="95"/>
-      <x:c r="N67" s="95"/>
-      <x:c r="O67" s="95"/>
-      <x:c r="P67" s="95"/>
-      <x:c r="Q67" s="95"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="90"/>
-      <x:c r="B68" s="90"/>
-      <x:c r="C68" s="90"/>
-      <x:c r="D68" s="90"/>
-      <x:c r="E68" s="90"/>
-      <x:c r="F68" s="95"/>
-      <x:c r="G68" s="95"/>
-      <x:c r="H68" s="95"/>
-      <x:c r="I68" s="90"/>
-      <x:c r="J68" s="90"/>
-      <x:c r="K68" s="95"/>
-      <x:c r="L68" s="95"/>
-      <x:c r="M68" s="95"/>
-      <x:c r="N68" s="95"/>
-      <x:c r="O68" s="95"/>
-      <x:c r="P68" s="95"/>
-      <x:c r="Q68" s="95"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="90"/>
-      <x:c r="B69" s="90"/>
-      <x:c r="C69" s="90"/>
-      <x:c r="D69" s="90"/>
-      <x:c r="E69" s="90"/>
-      <x:c r="F69" s="95"/>
-      <x:c r="G69" s="95"/>
-      <x:c r="H69" s="95"/>
-      <x:c r="I69" s="90"/>
-      <x:c r="J69" s="90"/>
-      <x:c r="K69" s="95"/>
-      <x:c r="L69" s="95"/>
-      <x:c r="M69" s="95"/>
-      <x:c r="N69" s="95"/>
-      <x:c r="O69" s="95"/>
-      <x:c r="P69" s="95"/>
-      <x:c r="Q69" s="95"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="90"/>
-      <x:c r="B70" s="90"/>
-      <x:c r="C70" s="90"/>
-      <x:c r="D70" s="90"/>
-      <x:c r="E70" s="90"/>
-      <x:c r="F70" s="95"/>
-      <x:c r="G70" s="95"/>
-      <x:c r="H70" s="95"/>
-      <x:c r="I70" s="90"/>
-      <x:c r="J70" s="90"/>
-      <x:c r="K70" s="95"/>
-      <x:c r="L70" s="95"/>
-      <x:c r="M70" s="95"/>
-      <x:c r="N70" s="95"/>
-      <x:c r="O70" s="95"/>
-      <x:c r="P70" s="95"/>
-      <x:c r="Q70" s="95"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="90"/>
-      <x:c r="B71" s="90"/>
-      <x:c r="C71" s="90"/>
-      <x:c r="D71" s="90"/>
-      <x:c r="E71" s="90"/>
-      <x:c r="F71" s="95"/>
-      <x:c r="G71" s="95"/>
-      <x:c r="H71" s="95"/>
-      <x:c r="I71" s="90"/>
-      <x:c r="J71" s="90"/>
-      <x:c r="K71" s="95"/>
-      <x:c r="L71" s="95"/>
-      <x:c r="M71" s="95"/>
-      <x:c r="N71" s="95"/>
-      <x:c r="O71" s="95"/>
-      <x:c r="P71" s="95"/>
-      <x:c r="Q71" s="95"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="90"/>
-      <x:c r="B72" s="90"/>
-      <x:c r="C72" s="90"/>
-      <x:c r="D72" s="90"/>
-      <x:c r="E72" s="90"/>
-      <x:c r="F72" s="95"/>
-      <x:c r="G72" s="95"/>
-      <x:c r="H72" s="95"/>
-      <x:c r="I72" s="90"/>
-      <x:c r="J72" s="90"/>
-      <x:c r="K72" s="95"/>
-      <x:c r="L72" s="95"/>
-      <x:c r="M72" s="95"/>
-      <x:c r="N72" s="95"/>
-      <x:c r="O72" s="95"/>
-      <x:c r="P72" s="95"/>
-      <x:c r="Q72" s="95"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="90"/>
-      <x:c r="B73" s="90"/>
-      <x:c r="C73" s="90"/>
-      <x:c r="D73" s="90"/>
-      <x:c r="E73" s="90"/>
-      <x:c r="F73" s="95"/>
-      <x:c r="G73" s="95"/>
-      <x:c r="H73" s="95"/>
-      <x:c r="I73" s="90"/>
-      <x:c r="J73" s="90"/>
-      <x:c r="K73" s="95"/>
-      <x:c r="L73" s="95"/>
-      <x:c r="M73" s="95"/>
-      <x:c r="N73" s="95"/>
-      <x:c r="O73" s="95"/>
-      <x:c r="P73" s="95"/>
-      <x:c r="Q73" s="95"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="90"/>
-      <x:c r="B74" s="90"/>
-      <x:c r="C74" s="90"/>
-      <x:c r="D74" s="90"/>
-      <x:c r="E74" s="90"/>
-      <x:c r="F74" s="95"/>
-      <x:c r="G74" s="95"/>
-      <x:c r="H74" s="95"/>
-      <x:c r="I74" s="90"/>
-      <x:c r="J74" s="90"/>
-      <x:c r="K74" s="95"/>
-      <x:c r="L74" s="95"/>
-      <x:c r="M74" s="95"/>
-      <x:c r="N74" s="95"/>
-      <x:c r="O74" s="95"/>
-      <x:c r="P74" s="95"/>
-      <x:c r="Q74" s="95"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="90"/>
-      <x:c r="B75" s="90"/>
-      <x:c r="C75" s="90"/>
-      <x:c r="D75" s="90"/>
-      <x:c r="E75" s="90"/>
-      <x:c r="F75" s="95"/>
-      <x:c r="G75" s="95"/>
-      <x:c r="H75" s="95"/>
-      <x:c r="I75" s="90"/>
-      <x:c r="J75" s="90"/>
-      <x:c r="K75" s="95"/>
-      <x:c r="L75" s="95"/>
-      <x:c r="M75" s="95"/>
-      <x:c r="N75" s="95"/>
-      <x:c r="O75" s="95"/>
-      <x:c r="P75" s="95"/>
-      <x:c r="Q75" s="95"/>
+    <x:row r="67" ht="72" customHeight="1">
+      <x:c r="A67" s="90" t="str">
+        <x:v>GAP-P1-CREATE-009</x:v>
+      </x:c>
+      <x:c r="B67" s="90" t="str">
+        <x:v>P1-CREATE-01</x:v>
+      </x:c>
+      <x:c r="C67" s="90" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D67" s="90" t="str">
+        <x:v>Work Item Create</x:v>
+      </x:c>
+      <x:c r="E67" s="90" t="str">
+        <x:v>Default Schedule/Flow State on create</x:v>
+      </x:c>
+      <x:c r="F67" s="95" t="str">
+        <x:v>A newly created Story/Defect defaults Schedule State and Flow State to Idea.</x:v>
+      </x:c>
+      <x:c r="G67" s="95" t="str">
+        <x:v>Mockup US-4822 defaulted new items to Idea.</x:v>
+      </x:c>
+      <x:c r="H67" s="95" t="str">
+        <x:v>DevInt US-8 (DEVINT-AUDIT CREATE 20260723) was created with Schedule State and Flow State = Defined, not Idea.</x:v>
+      </x:c>
+      <x:c r="I67" s="90" t="str">
+        <x:v>Business Rule</x:v>
+      </x:c>
+      <x:c r="J67" s="90" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K67" s="95" t="str">
+        <x:v>Default new Work Item Schedule State and Flow State to Idea on create, in both quick-create and detail.</x:v>
+      </x:c>
+      <x:c r="L67" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M67" s="95" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N67" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O67" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P67" s="95" t="str">
+        <x:v>retest 2026-07-23</x:v>
+      </x:c>
+      <x:c r="Q67" s="95" t="str">
+        <x:v>Newly testable after create was fixed. BA confirmed default must be Idea on 2026-07-23.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="72" customHeight="1">
+      <x:c r="A68" s="90" t="str">
+        <x:v>GAP-P1-TEAM-001</x:v>
+      </x:c>
+      <x:c r="B68" s="90" t="str">
+        <x:v>P1-TEAM-02</x:v>
+      </x:c>
+      <x:c r="C68" s="90" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D68" s="90" t="str">
+        <x:v>Settings &gt; Teams / Create Team</x:v>
+      </x:c>
+      <x:c r="E68" s="90" t="str">
+        <x:v>Team Lead requiredness contract</x:v>
+      </x:c>
+      <x:c r="F68" s="95" t="str">
+        <x:v>Create Team validates required fields client-side; if Lead is required it is enforced and shown before submit; a failed submit keeps the modal open with an actionable error.</x:v>
+      </x:c>
+      <x:c r="G68" s="95" t="str">
+        <x:v>Mockup Create Team defines the team form fields.</x:v>
+      </x:c>
+      <x:c r="H68" s="95" t="str">
+        <x:v>DevInt allows No lead and submits, but backend returns 422 VALIDATION_FAILED (leadId expected string, received null). The modal closes with no error message and no Team is created.</x:v>
+      </x:c>
+      <x:c r="I68" s="90" t="str">
+        <x:v>Functional / Validation / Contract</x:v>
+      </x:c>
+      <x:c r="J68" s="90" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K68" s="95" t="str">
+        <x:v>Align FE and backend: either make Team Lead required with client validation + inline error, or accept null leadId server-side. Replace the silent 422 with a field-level error and keep the modal open on failure.</x:v>
+      </x:c>
+      <x:c r="L68" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M68" s="95" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N68" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O68" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P68" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q68" s="95" t="str">
+        <x:v>Found 2026-07-24 during Team E2E create test (DEVINT-AUDIT Team, key DEVINTAUDI, project NXP, no lead). BA directed to pass and log for dev.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="72" customHeight="1">
+      <x:c r="A69" s="90" t="str">
+        <x:v>GAP-P1-HIST-001</x:v>
+      </x:c>
+      <x:c r="B69" s="90" t="str">
+        <x:v>P1-HIST-01</x:v>
+      </x:c>
+      <x:c r="C69" s="90" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D69" s="90" t="str">
+        <x:v>Work Item Detail / Revision History</x:v>
+      </x:c>
+      <x:c r="E69" s="90" t="str">
+        <x:v>State-change activity labeling / duplicate</x:v>
+      </x:c>
+      <x:c r="F69" s="95" t="str">
+        <x:v>Schedule State and Flow State changes log as distinct, correctly-labeled actions (schedule_state_changed vs flow_state_changed); a single change does not create duplicate rows.</x:v>
+      </x:c>
+      <x:c r="G69" s="95" t="str">
+        <x:v>SRS activity model uses distinct action codes per field (ACT-FR-005).</x:v>
+      </x:c>
+      <x:c r="H69" s="95" t="str">
+        <x:v>On US-8 each state change (via Task roll-up) produced two identical rows both labeled "Schedule State changed from X to Y". The Flow State change is mislabeled as Schedule State or duplicated.</x:v>
+      </x:c>
+      <x:c r="I69" s="90" t="str">
+        <x:v>Functional / Activity Log</x:v>
+      </x:c>
+      <x:c r="J69" s="90" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K69" s="95" t="str">
+        <x:v>Log Schedule and Flow changes as separate correctly-labeled actions; avoid duplicate entries for a single mutation.</x:v>
+      </x:c>
+      <x:c r="L69" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M69" s="95" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N69" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O69" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P69" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q69" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P1-HIST-01. BA confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="72" customHeight="1">
+      <x:c r="A70" s="90" t="str">
+        <x:v>GAP-P1-HIST-002</x:v>
+      </x:c>
+      <x:c r="B70" s="90" t="str">
+        <x:v>P1-HIST-01</x:v>
+      </x:c>
+      <x:c r="C70" s="90" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D70" s="90" t="str">
+        <x:v>Task Detail / Revision History</x:v>
+      </x:c>
+      <x:c r="E70" s="90" t="str">
+        <x:v>Task-level activity not logged</x:v>
+      </x:c>
+      <x:c r="F70" s="95" t="str">
+        <x:v>Task Revision History logs task.created, task.state_changed and task time updates for the Task (ACT-FR-002/005).</x:v>
+      </x:c>
+      <x:c r="G70" s="95" t="str">
+        <x:v>SRS requires Task Detail Revision History with task activity.</x:v>
+      </x:c>
+      <x:c r="H70" s="95" t="str">
+        <x:v>TA-6 Task Revision History shows "No activity recorded yet" despite task create, state changes (Complete then reopen) and time set. Task events appear only in the parent Work Item history.</x:v>
+      </x:c>
+      <x:c r="I70" s="90" t="str">
+        <x:v>Functional / Activity Log</x:v>
+      </x:c>
+      <x:c r="J70" s="90" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K70" s="95" t="str">
+        <x:v>Write task-level activity rows (create/state/time) to the Task activity log and show them in Task Revision History.</x:v>
+      </x:c>
+      <x:c r="L70" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M70" s="95" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N70" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O70" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P70" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q70" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P1-HIST-01. BA confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="72" customHeight="1">
+      <x:c r="A71" s="90" t="str">
+        <x:v>GAP-P2-IT-001</x:v>
+      </x:c>
+      <x:c r="B71" s="90" t="str">
+        <x:v>P2-IT-01</x:v>
+      </x:c>
+      <x:c r="C71" s="90" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D71" s="90" t="str">
+        <x:v>Timeboxes &gt; Iterations list</x:v>
+      </x:c>
+      <x:c r="E71" s="90" t="str">
+        <x:v>Missing Project and Task Estimate columns</x:v>
+      </x:c>
+      <x:c r="F71" s="95" t="str">
+        <x:v>Iterations list shows Name, Theme, Start Date, End Date, Project, Planned Velocity, Task Estimate and State (P2-IT-FR-005).</x:v>
+      </x:c>
+      <x:c r="G71" s="95" t="str">
+        <x:v>Mockup IterationsPage declares project and taskEstimate in its column set.</x:v>
+      </x:c>
+      <x:c r="H71" s="95" t="str">
+        <x:v>DevInt list shows ID, Name, Theme, Start Date, End Date, Planned Velocity and State only. Project and Task Estimate are absent.</x:v>
+      </x:c>
+      <x:c r="I71" s="90" t="str">
+        <x:v>Functional Display</x:v>
+      </x:c>
+      <x:c r="J71" s="90" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K71" s="95" t="str">
+        <x:v>Add the Project and Task Estimate columns to the Iterations list using the existing list contract.</x:v>
+      </x:c>
+      <x:c r="L71" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M71" s="95" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N71" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O71" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P71" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q71" s="95" t="str">
+        <x:v>Confirmed by both SRS FR-005 and the mockup column set.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="72" customHeight="1">
+      <x:c r="A72" s="90" t="str">
+        <x:v>GAP-P2-IS-003</x:v>
+      </x:c>
+      <x:c r="B72" s="90" t="str">
+        <x:v>P2-IS-01</x:v>
+      </x:c>
+      <x:c r="C72" s="90" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D72" s="90" t="str">
+        <x:v>Iteration Status list</x:v>
+      </x:c>
+      <x:c r="E72" s="90" t="str">
+        <x:v>Missing Type column</x:v>
+      </x:c>
+      <x:c r="F72" s="95" t="str">
+        <x:v>List columns are checkbox, rank, ID, Type, Name, Schedule State, Iteration, Blocked, Plan Est, Task Est, To Do, Owner (P2-IS-FR-018).</x:v>
+      </x:c>
+      <x:c r="G72" s="95" t="str">
+        <x:v>Mockup Iteration Status shows the work item Type.</x:v>
+      </x:c>
+      <x:c r="H72" s="95" t="str">
+        <x:v>DevInt list has no Type column; it also adds Feature, Blocked Reason, Tasks, Actual, Defect Status, Milestones and Dev Owner beyond the contract.</x:v>
+      </x:c>
+      <x:c r="I72" s="90" t="str">
+        <x:v>UI / Business</x:v>
+      </x:c>
+      <x:c r="J72" s="90" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K72" s="95" t="str">
+        <x:v>Add the Type column; review the extra columns against the approved contract or make them opt-in via Show Fields.</x:v>
+      </x:c>
+      <x:c r="L72" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M72" s="95" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N72" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O72" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P72" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q72" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P2-IS-01.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="72" customHeight="1">
+      <x:c r="A73" s="90" t="str">
+        <x:v>GAP-P2-IS-004</x:v>
+      </x:c>
+      <x:c r="B73" s="90" t="str">
+        <x:v>P2-IS-01</x:v>
+      </x:c>
+      <x:c r="C73" s="90" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D73" s="90" t="str">
+        <x:v>Iteration Status list</x:v>
+      </x:c>
+      <x:c r="E73" s="90" t="str">
+        <x:v>Forbidden per-row Defects column</x:v>
+      </x:c>
+      <x:c r="F73" s="95" t="str">
+        <x:v>The list must not include a per-row Defects column (P2-IS-FR-019). Defects is a summary metric only.</x:v>
+      </x:c>
+      <x:c r="G73" s="95" t="str">
+        <x:v>Mockup Iteration Status has no per-row Defects column.</x:v>
+      </x:c>
+      <x:c r="H73" s="95" t="str">
+        <x:v>DevInt list renders a per-row Defects column plus Defect Status.</x:v>
+      </x:c>
+      <x:c r="I73" s="90" t="str">
+        <x:v>UI / Business</x:v>
+      </x:c>
+      <x:c r="J73" s="90" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K73" s="95" t="str">
+        <x:v>Remove the per-row Defects column; keep Defects as the summary metric only.</x:v>
+      </x:c>
+      <x:c r="L73" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M73" s="95" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N73" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O73" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P73" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q73" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P2-IS-01.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="72" customHeight="1">
+      <x:c r="A74" s="90" t="str">
+        <x:v>GAP-P2-IS-005</x:v>
+      </x:c>
+      <x:c r="B74" s="90" t="str">
+        <x:v>P2-IS-01</x:v>
+      </x:c>
+      <x:c r="C74" s="90" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D74" s="90" t="str">
+        <x:v>Iteration Status</x:v>
+      </x:c>
+      <x:c r="E74" s="90" t="str">
+        <x:v>Board view toggle exposed</x:v>
+      </x:c>
+      <x:c r="F74" s="95" t="str">
+        <x:v>Iteration Board / Team Board are Future Backlog and absent from active navigation per the reconciled source of truth.</x:v>
+      </x:c>
+      <x:c r="G74" s="95" t="str">
+        <x:v>Mockup Track scope for Phase 2 is Iteration Status only.</x:v>
+      </x:c>
+      <x:c r="H74" s="95" t="str">
+        <x:v>DevInt Iteration Status exposes a List / Board toggle.</x:v>
+      </x:c>
+      <x:c r="I74" s="90" t="str">
+        <x:v>Scope Leakage</x:v>
+      </x:c>
+      <x:c r="J74" s="90" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K74" s="95" t="str">
+        <x:v>Hide the Board toggle until the board scope is approved, or get BA approval to bring board execution into scope.</x:v>
+      </x:c>
+      <x:c r="L74" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M74" s="95" t="str">
+        <x:v>FE / Scope</x:v>
+      </x:c>
+      <x:c r="N74" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O74" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P74" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q74" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P2-IS-01.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="72" customHeight="1">
+      <x:c r="A75" s="90" t="str">
+        <x:v>GAP-P2-BL-001</x:v>
+      </x:c>
+      <x:c r="B75" s="90" t="str">
+        <x:v>P2-BL-01</x:v>
+      </x:c>
+      <x:c r="C75" s="90" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D75" s="90" t="str">
+        <x:v>Backlog bulk actions</x:v>
+      </x:c>
+      <x:c r="E75" s="90" t="str">
+        <x:v>Missing bulk assign Release/Iteration; unexpected Delete/Copy</x:v>
+      </x:c>
+      <x:c r="F75" s="95" t="str">
+        <x:v>With rows selected the bar offers bulk assign Release (P2-BL-FR-015) and bulk assign Iteration (P2-BL-FR-015A).</x:v>
+      </x:c>
+      <x:c r="G75" s="95" t="str">
+        <x:v>Mockup selected bar exposes release and iteration selects.</x:v>
+      </x:c>
+      <x:c r="H75" s="95" t="str">
+        <x:v>DevInt selection bar shows only Delete and Copy. Bulk assign Release and Iteration are absent; Delete and Copy are not part of the P2.1 bulk contract.</x:v>
+      </x:c>
+      <x:c r="I75" s="90" t="str">
+        <x:v>Functional / Scope</x:v>
+      </x:c>
+      <x:c r="J75" s="90" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K75" s="95" t="str">
+        <x:v>Add bulk assign Release and Iteration to the selected bar. Get BA decision on whether bulk Delete/Copy stay in scope and, if kept, define soft-delete and permission rules.</x:v>
+      </x:c>
+      <x:c r="L75" s="95" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="M75" s="95" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N75" s="95" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O75" s="95" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P75" s="95" t="str">
+        <x:v>2026-07-24 audit</x:v>
+      </x:c>
+      <x:c r="Q75" s="95" t="str">
+        <x:v>Found 2026-07-24 auditing P2-BL-01. Manage Filters remains Accepted As-Is / Future Backlog.</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="90"/>
-      <x:c r="B76" s="90"/>
-      <x:c r="C76" s="90"/>
-      <x:c r="D76" s="90"/>
-      <x:c r="E76" s="90"/>
-      <x:c r="F76" s="95"/>
-      <x:c r="G76" s="95"/>
-      <x:c r="H76" s="95"/>
-      <x:c r="I76" s="90"/>
-      <x:c r="J76" s="90"/>
-      <x:c r="K76" s="95"/>
-      <x:c r="L76" s="95"/>
-      <x:c r="M76" s="95"/>
-      <x:c r="N76" s="95"/>
-      <x:c r="O76" s="95"/>
-      <x:c r="P76" s="95"/>
-      <x:c r="Q76" s="95"/>
+      <x:c r="A76" s="91" t="str">
+        <x:v>GAP-P3-TS-001</x:v>
+      </x:c>
+      <x:c r="B76" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C76" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D76" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E76" s="91" t="str">
+        <x:v>Local search input</x:v>
+      </x:c>
+      <x:c r="F76" s="92" t="str">
+        <x:v>SRS FR-006 requires Team Status to not show a local search input.</x:v>
+      </x:c>
+      <x:c r="G76" s="92" t="str">
+        <x:v>TeamStatusPage.tsx renders no search box; only the Iteration selector row and the dense table.</x:v>
+      </x:c>
+      <x:c r="H76" s="92" t="str">
+        <x:v>DevInt Track &gt; Team Status shows a Search Tasks search input above the table.</x:v>
+      </x:c>
+      <x:c r="I76" s="91" t="str">
+        <x:v>Functional / UI</x:v>
+      </x:c>
+      <x:c r="J76" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K76" s="92" t="str">
+        <x:v>Remove the Team Status local search input to match the approved SRS/mockup.</x:v>
+      </x:c>
+      <x:c r="L76" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M76" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N76" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O76" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P76" s="92" t="str">
+        <x:v>DevInt Track &gt; Team Status, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q76" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="90"/>
-      <x:c r="B77" s="90"/>
-      <x:c r="C77" s="90"/>
-      <x:c r="D77" s="90"/>
-      <x:c r="E77" s="90"/>
-      <x:c r="F77" s="95"/>
-      <x:c r="G77" s="95"/>
-      <x:c r="H77" s="95"/>
-      <x:c r="I77" s="90"/>
-      <x:c r="J77" s="90"/>
-      <x:c r="K77" s="95"/>
-      <x:c r="L77" s="95"/>
-      <x:c r="M77" s="95"/>
-      <x:c r="N77" s="95"/>
-      <x:c r="O77" s="95"/>
-      <x:c r="P77" s="95"/>
-      <x:c r="Q77" s="95"/>
+      <x:c r="A77" s="91" t="str">
+        <x:v>GAP-P3-TS-002</x:v>
+      </x:c>
+      <x:c r="B77" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C77" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D77" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E77" s="91" t="str">
+        <x:v>Filters/Show Fields/pagination controls</x:v>
+      </x:c>
+      <x:c r="F77" s="92" t="str">
+        <x:v>SRS section 7 screen mapping lists only the Iteration selector plus dense table with totals row; no Filters, Show Fields or pagination.</x:v>
+      </x:c>
+      <x:c r="G77" s="92" t="str">
+        <x:v>TeamStatusPage.tsx renders none of these controls.</x:v>
+      </x:c>
+      <x:c r="H77" s="92" t="str">
+        <x:v>DevInt shows a Filters button, a Show Fields button and full pagination (Rows per page, Page X of Y) copied from the Iteration Status/Backlog template.</x:v>
+      </x:c>
+      <x:c r="I77" s="91" t="str">
+        <x:v>Functional / UI</x:v>
+      </x:c>
+      <x:c r="J77" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K77" s="92" t="str">
+        <x:v>Remove Filters/Show Fields/pagination from Team Status, or get explicit BA sign-off if this is an intentional deviation from the approved mockup.</x:v>
+      </x:c>
+      <x:c r="L77" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M77" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N77" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O77" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P77" s="92" t="str">
+        <x:v>DevInt Track &gt; Team Status, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q77" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="90"/>
-      <x:c r="B78" s="90"/>
-      <x:c r="C78" s="90"/>
-      <x:c r="D78" s="90"/>
-      <x:c r="E78" s="90"/>
-      <x:c r="F78" s="95"/>
-      <x:c r="G78" s="95"/>
-      <x:c r="H78" s="95"/>
-      <x:c r="I78" s="90"/>
-      <x:c r="J78" s="90"/>
-      <x:c r="K78" s="95"/>
-      <x:c r="L78" s="95"/>
-      <x:c r="M78" s="95"/>
-      <x:c r="N78" s="95"/>
-      <x:c r="O78" s="95"/>
-      <x:c r="P78" s="95"/>
-      <x:c r="Q78" s="95"/>
+      <x:c r="A78" s="91" t="str">
+        <x:v>GAP-P3-TS-003</x:v>
+      </x:c>
+      <x:c r="B78" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C78" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D78" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E78" s="91" t="str">
+        <x:v>Breadcrumb</x:v>
+      </x:c>
+      <x:c r="F78" s="92" t="str">
+        <x:v>FR-002: breadcrumb displays current Project, Track, and Team status.</x:v>
+      </x:c>
+      <x:c r="G78" s="92" t="str">
+        <x:v>Mockup shows Nexus Platform 2025 &gt; Track &gt; Team status.</x:v>
+      </x:c>
+      <x:c r="H78" s="92" t="str">
+        <x:v>DevInt breadcrumb shows ACME Corp &gt; Team Status only - uses the Org name instead of the Project name and drops the Track segment entirely.</x:v>
+      </x:c>
+      <x:c r="I78" s="91" t="str">
+        <x:v>Functional / Navigation</x:v>
+      </x:c>
+      <x:c r="J78" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K78" s="92" t="str">
+        <x:v>Fix breadcrumb to show [Project] &gt; Track &gt; Team status.</x:v>
+      </x:c>
+      <x:c r="L78" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M78" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N78" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O78" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P78" s="92" t="str">
+        <x:v>DevInt Track &gt; Team Status, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q78" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="90"/>
-      <x:c r="B79" s="90"/>
-      <x:c r="C79" s="90"/>
-      <x:c r="D79" s="90"/>
-      <x:c r="E79" s="90"/>
-      <x:c r="F79" s="95"/>
-      <x:c r="G79" s="95"/>
-      <x:c r="H79" s="95"/>
-      <x:c r="I79" s="90"/>
-      <x:c r="J79" s="90"/>
-      <x:c r="K79" s="95"/>
-      <x:c r="L79" s="95"/>
-      <x:c r="M79" s="95"/>
-      <x:c r="N79" s="95"/>
-      <x:c r="O79" s="95"/>
-      <x:c r="P79" s="95"/>
-      <x:c r="Q79" s="95"/>
+      <x:c r="A79" s="91" t="str">
+        <x:v>GAP-P3-TS-004</x:v>
+      </x:c>
+      <x:c r="B79" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C79" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D79" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E79" s="91" t="str">
+        <x:v>Parent auto-completion reopen rule</x:v>
+      </x:c>
+      <x:c r="F79" s="92" t="str">
+        <x:v>FR-041: reopening a Task after all child Tasks had been Completed must recalculate metrics and automatically set the parent Story/Defect status to In-Progress.</x:v>
+      </x:c>
+      <x:c r="G79" s="92" t="str">
+        <x:v>Mockup is local-state only and does not implement backend status automation.</x:v>
+      </x:c>
+      <x:c r="H79" s="92" t="str">
+        <x:v>Verified live on two cases. US-8/TA-6 (parent purely Completed): reopening TA-6 correctly reverts US-8 to In-Progress. US-11/TA-8 (parent already manually promoted to Accepted): reopening the only child Task TA-8 does NOT revert the parent; US-11 stays Accepted.</x:v>
+      </x:c>
+      <x:c r="I79" s="91" t="str">
+        <x:v>Business Rule</x:v>
+      </x:c>
+      <x:c r="J79" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K79" s="92" t="str">
+        <x:v>BA to confirm intended behavior - should reopening a Task always force the parent back to In-Progress even from Accepted, or is Accepted meant to be protected from this automation.</x:v>
+      </x:c>
+      <x:c r="L79" s="92" t="str">
+        <x:v>Fix Direction Approved</x:v>
+      </x:c>
+      <x:c r="M79" s="92" t="str">
+        <x:v>FE / Business Rule</x:v>
+      </x:c>
+      <x:c r="N79" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O79" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P79" s="92" t="str">
+        <x:v>DevInt Team Status + US-11/US-8 Work Item Detail, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q79" s="92" t="str">
+        <x:v>BA 2026-07-24: confirmed as a bug. Reopening a Task from an all-Completed parent must revert the parent to In-Progress EVEN when the parent was manually promoted to Accepted; Accepted is not protected from this automation. Dev to fix so the reopen roll-up applies from Accepted too.</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="90"/>
-      <x:c r="B80" s="90"/>
-      <x:c r="C80" s="90"/>
-      <x:c r="D80" s="90"/>
-      <x:c r="E80" s="90"/>
-      <x:c r="F80" s="95"/>
-      <x:c r="G80" s="95"/>
-      <x:c r="H80" s="95"/>
-      <x:c r="I80" s="90"/>
-      <x:c r="J80" s="90"/>
-      <x:c r="K80" s="95"/>
-      <x:c r="L80" s="95"/>
-      <x:c r="M80" s="95"/>
-      <x:c r="N80" s="95"/>
-      <x:c r="O80" s="95"/>
-      <x:c r="P80" s="95"/>
-      <x:c r="Q80" s="95"/>
+      <x:c r="A80" s="91" t="str">
+        <x:v>GAP-P3-TS-005</x:v>
+      </x:c>
+      <x:c r="B80" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C80" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D80" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E80" s="91" t="str">
+        <x:v>Task State control type</x:v>
+      </x:c>
+      <x:c r="F80" s="92" t="str">
+        <x:v>FR-021/022: Task State is an inline editable dropdown with exactly Defined, In-Progress, Completed.</x:v>
+      </x:c>
+      <x:c r="G80" s="92" t="str">
+        <x:v>TeamStatusPage.tsx ItemRow renders a native select element with the 3 full-text options.</x:v>
+      </x:c>
+      <x:c r="H80" s="92" t="str">
+        <x:v>DevInt renders a 3-segment icon toggle group instead of a dropdown; the 2 non-active segments render with transparent text so no label is visible, only the active segment shows a letter.</x:v>
+      </x:c>
+      <x:c r="I80" s="91" t="str">
+        <x:v>UI / UX</x:v>
+      </x:c>
+      <x:c r="J80" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K80" s="92" t="str">
+        <x:v>Match the approved dropdown control, or at minimum fix the toggle label visibility for the non-selected states.</x:v>
+      </x:c>
+      <x:c r="L80" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M80" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N80" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O80" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P80" s="92" t="str">
+        <x:v>DevInt Team Status, TA-7/TA-8 rows, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q80" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="90"/>
-      <x:c r="B81" s="90"/>
-      <x:c r="C81" s="90"/>
-      <x:c r="D81" s="90"/>
-      <x:c r="E81" s="90"/>
-      <x:c r="F81" s="95"/>
-      <x:c r="G81" s="95"/>
-      <x:c r="H81" s="95"/>
-      <x:c r="I81" s="90"/>
-      <x:c r="J81" s="90"/>
-      <x:c r="K81" s="95"/>
-      <x:c r="L81" s="95"/>
-      <x:c r="M81" s="95"/>
-      <x:c r="N81" s="95"/>
-      <x:c r="O81" s="95"/>
-      <x:c r="P81" s="95"/>
-      <x:c r="Q81" s="95"/>
+      <x:c r="A81" s="91" t="str">
+        <x:v>GAP-P3-TS-006</x:v>
+      </x:c>
+      <x:c r="B81" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C81" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D81" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E81" s="91" t="str">
+        <x:v>Estimate/ToDo/Actuals default display</x:v>
+      </x:c>
+      <x:c r="F81" s="92" t="str">
+        <x:v>SRS 8.3: Estimate, ToDo and Actuals default to 0 when not set.</x:v>
+      </x:c>
+      <x:c r="G81" s="92" t="str">
+        <x:v>Mock data always seeds numeric task hours; no null case shown in mockup.</x:v>
+      </x:c>
+      <x:c r="H81" s="92" t="str">
+        <x:v>Task row TA-10 (no estimate/todo/actual data) displays an em-dash in all three columns instead of 0.</x:v>
+      </x:c>
+      <x:c r="I81" s="91" t="str">
+        <x:v>Functional / Data</x:v>
+      </x:c>
+      <x:c r="J81" s="91" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="K81" s="92" t="str">
+        <x:v>Default missing Estimate/ToDo/Actuals to 0 instead of a dash placeholder.</x:v>
+      </x:c>
+      <x:c r="L81" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M81" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N81" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O81" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P81" s="92" t="str">
+        <x:v>DevInt Team Status, TA-10 row, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q81" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="90"/>
-      <x:c r="B82" s="90"/>
-      <x:c r="C82" s="90"/>
-      <x:c r="D82" s="90"/>
-      <x:c r="E82" s="90"/>
-      <x:c r="F82" s="95"/>
-      <x:c r="G82" s="95"/>
-      <x:c r="H82" s="95"/>
-      <x:c r="I82" s="90"/>
-      <x:c r="J82" s="90"/>
-      <x:c r="K82" s="95"/>
-      <x:c r="L82" s="95"/>
-      <x:c r="M82" s="95"/>
-      <x:c r="N82" s="95"/>
-      <x:c r="O82" s="95"/>
-      <x:c r="P82" s="95"/>
-      <x:c r="Q82" s="95"/>
+      <x:c r="A82" s="91" t="str">
+        <x:v>GAP-P3-TS-007</x:v>
+      </x:c>
+      <x:c r="B82" s="91" t="str">
+        <x:v>P3-TS-01</x:v>
+      </x:c>
+      <x:c r="C82" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D82" s="91" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="E82" s="91" t="str">
+        <x:v>Task Dashboard state labels</x:v>
+      </x:c>
+      <x:c r="F82" s="92" t="str">
+        <x:v>FR-022/038: Task State values are exactly Defined, In-Progress, Completed.</x:v>
+      </x:c>
+      <x:c r="G82" s="92" t="str">
+        <x:v>Mockup consistently uses the full labels.</x:v>
+      </x:c>
+      <x:c r="H82" s="92" t="str">
+        <x:v>Work Item Detail Tasks tab state buttons are labeled Define, In Progress, Complete instead of the exact catalog wording.</x:v>
+      </x:c>
+      <x:c r="I82" s="91" t="str">
+        <x:v>UI Copy</x:v>
+      </x:c>
+      <x:c r="J82" s="91" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="K82" s="92" t="str">
+        <x:v>Correct the button labels to Defined / In-Progress / Completed.</x:v>
+      </x:c>
+      <x:c r="L82" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M82" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N82" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O82" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P82" s="92" t="str">
+        <x:v>DevInt US-8/US-11 Work Item Detail Tasks tab, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q82" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="90"/>
-      <x:c r="B83" s="90"/>
-      <x:c r="C83" s="90"/>
-      <x:c r="D83" s="90"/>
-      <x:c r="E83" s="90"/>
-      <x:c r="F83" s="95"/>
-      <x:c r="G83" s="95"/>
-      <x:c r="H83" s="95"/>
-      <x:c r="I83" s="90"/>
-      <x:c r="J83" s="90"/>
-      <x:c r="K83" s="95"/>
-      <x:c r="L83" s="95"/>
-      <x:c r="M83" s="95"/>
-      <x:c r="N83" s="95"/>
-      <x:c r="O83" s="95"/>
-      <x:c r="P83" s="95"/>
-      <x:c r="Q83" s="95"/>
+      <x:c r="A83" s="91" t="str">
+        <x:v>GAP-P3-REL-001</x:v>
+      </x:c>
+      <x:c r="B83" s="91" t="str">
+        <x:v>P3-REL-01</x:v>
+      </x:c>
+      <x:c r="C83" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D83" s="91" t="str">
+        <x:v>Release Detail</x:v>
+      </x:c>
+      <x:c r="E83" s="91" t="str">
+        <x:v>Release Progress widget</x:v>
+      </x:c>
+      <x:c r="F83" s="92" t="str">
+        <x:v>FR-037: Phase 3 Release list/detail must not add a Release Progress column or widget; Progress is deferred to Phase 5 Portfolio &gt; Release Planning.</x:v>
+      </x:c>
+      <x:c r="G83" s="92" t="str">
+        <x:v>ReleasesPage.tsx mockup has no burndown chart.</x:v>
+      </x:c>
+      <x:c r="H83" s="92" t="str">
+        <x:v>DevInt Release detail (RE-2) shows a Burndown section with a chart placeholder below the Task Roll-up panel.</x:v>
+      </x:c>
+      <x:c r="I83" s="91" t="str">
+        <x:v>Business Rule / Scope Leakage</x:v>
+      </x:c>
+      <x:c r="J83" s="91" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K83" s="92" t="str">
+        <x:v>Remove the Burndown widget from Release detail for Phase 3.2; defer to Phase 5 Release Planning per SRS.</x:v>
+      </x:c>
+      <x:c r="L83" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M83" s="92" t="str">
+        <x:v>FE / Scope</x:v>
+      </x:c>
+      <x:c r="N83" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O83" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P83" s="92" t="str">
+        <x:v>DevInt Release Detail RE-2, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q83" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="90"/>
-      <x:c r="B84" s="90"/>
-      <x:c r="C84" s="90"/>
-      <x:c r="D84" s="90"/>
-      <x:c r="E84" s="90"/>
-      <x:c r="F84" s="95"/>
-      <x:c r="G84" s="95"/>
-      <x:c r="H84" s="95"/>
-      <x:c r="I84" s="90"/>
-      <x:c r="J84" s="90"/>
-      <x:c r="K84" s="95"/>
-      <x:c r="L84" s="95"/>
-      <x:c r="M84" s="95"/>
-      <x:c r="N84" s="95"/>
-      <x:c r="O84" s="95"/>
-      <x:c r="P84" s="95"/>
-      <x:c r="Q84" s="95"/>
+      <x:c r="A84" s="91" t="str">
+        <x:v>GAP-P3-REL-002</x:v>
+      </x:c>
+      <x:c r="B84" s="91" t="str">
+        <x:v>P3-REL-02</x:v>
+      </x:c>
+      <x:c r="C84" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D84" s="91" t="str">
+        <x:v>Release Artifacts</x:v>
+      </x:c>
+      <x:c r="E84" s="91" t="str">
+        <x:v>Release Artifacts assignment display</x:v>
+      </x:c>
+      <x:c r="F84" s="92" t="str">
+        <x:v>FR-029/032: Release Artifacts view shows the Story/Defect work items assigned to the Release.</x:v>
+      </x:c>
+      <x:c r="G84" s="92" t="str">
+        <x:v>Mockup local state appends the assigned item to the Release artifact list immediately on assignment.</x:v>
+      </x:c>
+      <x:c r="H84" s="92" t="str">
+        <x:v>Assigned US-11 to RE-2 from the Backlog Release picker; Backlog Release column and the Release list Task Est. roll-up both updated correctly (6h), but RE-2 Artifacts tab still showed No artifacts linked to this release even after a hard page reload.</x:v>
+      </x:c>
+      <x:c r="I84" s="91" t="str">
+        <x:v>Functional / Data</x:v>
+      </x:c>
+      <x:c r="J84" s="91" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="K84" s="92" t="str">
+        <x:v>Fix the Release Artifacts query so it returns work items whose Release assignment matches; this blocks all reassignment-refresh testing (FR-031/036/038) until fixed.</x:v>
+      </x:c>
+      <x:c r="L84" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M84" s="92" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N84" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O84" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P84" s="92" t="str">
+        <x:v>DevInt Release Detail RE-2 &gt; Artifacts, US-11 assignment, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q84" s="92" t="str">
+        <x:v>US-11 restored to unassigned/Accepted after the test.</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="90"/>
-      <x:c r="B85" s="90"/>
-      <x:c r="C85" s="90"/>
-      <x:c r="D85" s="90"/>
-      <x:c r="E85" s="90"/>
-      <x:c r="F85" s="95"/>
-      <x:c r="G85" s="95"/>
-      <x:c r="H85" s="95"/>
-      <x:c r="I85" s="90"/>
-      <x:c r="J85" s="90"/>
-      <x:c r="K85" s="95"/>
-      <x:c r="L85" s="95"/>
-      <x:c r="M85" s="95"/>
-      <x:c r="N85" s="95"/>
-      <x:c r="O85" s="95"/>
-      <x:c r="P85" s="95"/>
-      <x:c r="Q85" s="95"/>
+      <x:c r="A85" s="91" t="str">
+        <x:v>GAP-P3-MS-001</x:v>
+      </x:c>
+      <x:c r="B85" s="91" t="str">
+        <x:v>P3-MS-03</x:v>
+      </x:c>
+      <x:c r="C85" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D85" s="91" t="str">
+        <x:v>Milestone Artifacts</x:v>
+      </x:c>
+      <x:c r="E85" s="91" t="str">
+        <x:v>Add Artifact control</x:v>
+      </x:c>
+      <x:c r="F85" s="92" t="str">
+        <x:v>FR-028: Add Artifact follows the Backlog Story/Defect create/picker pattern and appends the current Milestone relationship.</x:v>
+      </x:c>
+      <x:c r="G85" s="92" t="str">
+        <x:v>Mockup checklist item M5.3 confirms Milestone Artifacts should support assigning Story/Defect work items.</x:v>
+      </x:c>
+      <x:c r="H85" s="92" t="str">
+        <x:v>MS-2 Artifacts tab shows only a search box and a No artifacts linked to this milestone empty state; there is no Add Artifact button or control anywhere on the tab.</x:v>
+      </x:c>
+      <x:c r="I85" s="91" t="str">
+        <x:v>Functional / Scope</x:v>
+      </x:c>
+      <x:c r="J85" s="91" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="K85" s="92" t="str">
+        <x:v>Implement the Add Artifact control on the Milestone Artifacts tab following the Backlog picker pattern.</x:v>
+      </x:c>
+      <x:c r="L85" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M85" s="92" t="str">
+        <x:v>FE</x:v>
+      </x:c>
+      <x:c r="N85" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O85" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P85" s="92" t="str">
+        <x:v>DevInt Milestone Detail MS-2 &gt; Artifacts, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q85" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="90"/>
-      <x:c r="B86" s="90"/>
-      <x:c r="C86" s="90"/>
-      <x:c r="D86" s="90"/>
-      <x:c r="E86" s="90"/>
-      <x:c r="F86" s="95"/>
-      <x:c r="G86" s="95"/>
-      <x:c r="H86" s="95"/>
-      <x:c r="I86" s="90"/>
-      <x:c r="J86" s="90"/>
-      <x:c r="K86" s="95"/>
-      <x:c r="L86" s="95"/>
-      <x:c r="M86" s="95"/>
-      <x:c r="N86" s="95"/>
-      <x:c r="O86" s="95"/>
-      <x:c r="P86" s="95"/>
-      <x:c r="Q86" s="95"/>
+      <x:c r="A86" s="91" t="str">
+        <x:v>GAP-P3-MS-002</x:v>
+      </x:c>
+      <x:c r="B86" s="91" t="str">
+        <x:v>P3-MS-03</x:v>
+      </x:c>
+      <x:c r="C86" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D86" s="91" t="str">
+        <x:v>Work Item Detail</x:v>
+      </x:c>
+      <x:c r="E86" s="91" t="str">
+        <x:v>Work Item Milestone multi-select</x:v>
+      </x:c>
+      <x:c r="F86" s="92" t="str">
+        <x:v>FR-025: Work Item Milestone assignment uses a multi-select control; selected Milestones always remain visible.</x:v>
+      </x:c>
+      <x:c r="G86" s="92" t="str">
+        <x:v>Not covered in the Work Item Detail mockup component reviewed this session.</x:v>
+      </x:c>
+      <x:c r="H86" s="92" t="str">
+        <x:v>US-8 Work Item Detail right panel shows a Milestones row with static text No milestones - confirmed via accessibility tree that it has zero interactive control, not even a button.</x:v>
+      </x:c>
+      <x:c r="I86" s="91" t="str">
+        <x:v>Functional / Scope</x:v>
+      </x:c>
+      <x:c r="J86" s="91" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="K86" s="92" t="str">
+        <x:v>Implement the Milestone multi-select control on Work Item Detail. Combined with GAP-P3-MS-001, Milestone-to-Work-Item assignment is currently unreachable from both directions.</x:v>
+      </x:c>
+      <x:c r="L86" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M86" s="92" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N86" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O86" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P86" s="92" t="str">
+        <x:v>DevInt US-8 Work Item Detail, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q86" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="90"/>
-      <x:c r="B87" s="90"/>
-      <x:c r="C87" s="90"/>
-      <x:c r="D87" s="90"/>
-      <x:c r="E87" s="90"/>
-      <x:c r="F87" s="95"/>
-      <x:c r="G87" s="95"/>
-      <x:c r="H87" s="95"/>
-      <x:c r="I87" s="90"/>
-      <x:c r="J87" s="90"/>
-      <x:c r="K87" s="95"/>
-      <x:c r="L87" s="95"/>
-      <x:c r="M87" s="95"/>
-      <x:c r="N87" s="95"/>
-      <x:c r="O87" s="95"/>
-      <x:c r="P87" s="95"/>
-      <x:c r="Q87" s="95"/>
+      <x:c r="A87" s="91" t="str">
+        <x:v>GAP-P3-QA-001</x:v>
+      </x:c>
+      <x:c r="B87" s="91" t="str">
+        <x:v>P3-QA-01</x:v>
+      </x:c>
+      <x:c r="C87" s="91" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="D87" s="91" t="str">
+        <x:v>Quality/Defect</x:v>
+      </x:c>
+      <x:c r="E87" s="91" t="str">
+        <x:v>Create Defect from Quality</x:v>
+      </x:c>
+      <x:c r="F87" s="92" t="str">
+        <x:v>FR-006/AC-6: user can create a Defect from Quality &gt; Defect.</x:v>
+      </x:c>
+      <x:c r="G87" s="92" t="str">
+        <x:v>Mockup appends a new Defect row to local state immediately on submit.</x:v>
+      </x:c>
+      <x:c r="H87" s="92" t="str">
+        <x:v>Filled Name, Severity (Major Problem) and Priority (Normal) in the Quality &gt; Defect Add New modal and submitted; the modal closed with no visible error, but no new Defect row appeared and the Open Defects KPI stayed at 3. Reproduced twice, confirmed again after a fresh navigation.</x:v>
+      </x:c>
+      <x:c r="I87" s="91" t="str">
+        <x:v>Functional</x:v>
+      </x:c>
+      <x:c r="J87" s="91" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="K87" s="92" t="str">
+        <x:v>Fix Defect creation from the Quality &gt; Defect entry point; also verify Backlog-side Defect creation still works as a comparison point.</x:v>
+      </x:c>
+      <x:c r="L87" s="92" t="str">
+        <x:v>Gap Confirmed</x:v>
+      </x:c>
+      <x:c r="M87" s="92" t="str">
+        <x:v>FE / API</x:v>
+      </x:c>
+      <x:c r="N87" s="92" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O87" s="92" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="P87" s="92" t="str">
+        <x:v>DevInt Quality &gt; Defect, observed 2026-07-24</x:v>
+      </x:c>
+      <x:c r="Q87" s="92" t="str">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="90"/>
